--- a/results/job_matches_2026-10-11.xlsx
+++ b/results/job_matches_2026-10-11.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,52 +456,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data and AI Platform Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Murray, UT, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, PySpark, DynamoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f58b73435c41c623</t>
+          <t>https://www.indeed.com/viewjob?jk=a4383f4a43e40098</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Philadelphia, PA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -509,120 +509,50 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, PySpark, DynamoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4383f4a43e40098</t>
+          <t>https://www.indeed.com/viewjob?jk=5d221c596893433e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Healthcare)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Paytm One97 Communications</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, USA USA</t>
+          <t>Storden, MN, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d221c596893433e</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>New York, NY, USA USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d868e21430b8d97c</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Paytm One97 Communications</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Storden, MN, USA USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=de54c7ef6aacffc8</t>
         </is>

--- a/results/job_matches_2026-10-11.xlsx
+++ b/results/job_matches_2026-10-11.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Pittsburgh, PA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, PySpark, DynamoDB</t>
+          <t>AWS, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,24 +484,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4383f4a43e40098</t>
+          <t>https://www.indeed.com/viewjob?jk=89a4ee98072606c4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Healthcare)</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -509,50 +509,85 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, PySpark, DynamoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d221c596893433e</t>
+          <t>https://www.indeed.com/viewjob?jk=a4383f4a43e40098</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Innovya Technologies</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pasadena, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0abbf70775a0e95</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Paytm One97 Communications</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Storden, MN, USA USA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>10.4</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=de54c7ef6aacffc8</t>
         </is>

--- a/results/job_matches_2026-10-11.xlsx
+++ b/results/job_matches_2026-10-11.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior DevOps Engineer (Hub-Remote: DC or Philly Metro)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Element 84</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, USA USA</t>
+          <t>Alexandria, VA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, BigQuery, Spark</t>
+          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89a4ee98072606c4</t>
+          <t>https://www.indeed.com/viewjob?jk=cf2162b37870f256</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Pittsburgh, PA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, PySpark, DynamoDB</t>
+          <t>AWS, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4383f4a43e40098</t>
+          <t>https://www.indeed.com/viewjob?jk=89a4ee98072606c4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pasadena, CA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, PySpark, DynamoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,40 +554,75 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0abbf70775a0e95</t>
+          <t>https://www.indeed.com/viewjob?jk=a4383f4a43e40098</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Innovya Technologies</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pasadena, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0abbf70775a0e95</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Paytm One97 Communications</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Storden, MN, USA USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>10.4</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=de54c7ef6aacffc8</t>
         </is>
